--- a/Data/collapsed database manual cases/hidalgo_collapsed_edited.xlsx
+++ b/Data/collapsed database manual cases/hidalgo_collapsed_edited.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jpzorrilla/Documents/GitHub/The-Mexican-municipal-elections-electoral-precinct-level-database/Data/collapsed database manual cases/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C5238AC-1EE5-984F-B5E0-75845DDBFACD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{053FFEF8-1F42-C645-B392-58B6E13ACA96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="35840" windowHeight="22400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4480" yWindow="500" windowWidth="31360" windowHeight="21900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5687" uniqueCount="1380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5697" uniqueCount="1384">
   <si>
     <t>uniqueid</t>
   </si>
@@ -4163,13 +4163,25 @@
   </si>
   <si>
     <t>CI</t>
+  </si>
+  <si>
+    <t>PODEMOS</t>
+  </si>
+  <si>
+    <t>LIDIA TELLEZ CUENCA</t>
+  </si>
+  <si>
+    <t>HECTOR HUGO RAMIREZ LOPEZ</t>
+  </si>
+  <si>
+    <t>JAVIER SANTILLAN MELO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4202,6 +4214,12 @@
       <name val="Abadi"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -4229,7 +4247,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4240,6 +4258,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4545,7 +4564,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:S526"/>
+  <dimension ref="A1:S529"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.1640625" bestFit="1" customWidth="1"/>
@@ -28363,7 +28382,7 @@
         <v>1373</v>
       </c>
     </row>
-    <row r="513" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A513">
         <v>13076</v>
       </c>
@@ -28386,7 +28405,7 @@
         <v>1373</v>
       </c>
     </row>
-    <row r="514" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A514">
         <v>13077</v>
       </c>
@@ -28409,7 +28428,7 @@
         <v>1373</v>
       </c>
     </row>
-    <row r="515" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A515">
         <v>13002</v>
       </c>
@@ -28432,7 +28451,7 @@
         <v>1373</v>
       </c>
     </row>
-    <row r="516" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A516">
         <v>13003</v>
       </c>
@@ -28455,7 +28474,7 @@
         <v>1374</v>
       </c>
     </row>
-    <row r="517" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A517">
         <v>13011</v>
       </c>
@@ -28478,7 +28497,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="518" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A518">
         <v>13013</v>
       </c>
@@ -28501,7 +28520,7 @@
         <v>1375</v>
       </c>
     </row>
-    <row r="519" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A519">
         <v>13017</v>
       </c>
@@ -28518,7 +28537,7 @@
         <v>1365</v>
       </c>
     </row>
-    <row r="520" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A520">
         <v>13035</v>
       </c>
@@ -28541,7 +28560,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="521" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A521">
         <v>13040</v>
       </c>
@@ -28564,7 +28583,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="522" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A522">
         <v>13043</v>
       </c>
@@ -28587,7 +28606,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="523" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A523">
         <v>13047</v>
       </c>
@@ -28610,7 +28629,7 @@
         <v>1377</v>
       </c>
     </row>
-    <row r="524" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A524">
         <v>13050</v>
       </c>
@@ -28633,7 +28652,7 @@
         <v>1378</v>
       </c>
     </row>
-    <row r="525" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A525">
         <v>13059</v>
       </c>
@@ -28653,7 +28672,7 @@
         <v>1379</v>
       </c>
     </row>
-    <row r="526" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A526">
         <v>13076</v>
       </c>
@@ -28675,6 +28694,58 @@
       <c r="I526" t="s">
         <v>1372</v>
       </c>
+    </row>
+    <row r="527" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A527">
+        <v>13012</v>
+      </c>
+      <c r="B527">
+        <v>2024</v>
+      </c>
+      <c r="E527" t="s">
+        <v>1380</v>
+      </c>
+      <c r="F527" t="s">
+        <v>1381</v>
+      </c>
+      <c r="H527" t="s">
+        <v>1380</v>
+      </c>
+      <c r="J527" t="s">
+        <v>1380</v>
+      </c>
+      <c r="K527" t="s">
+        <v>1382</v>
+      </c>
+    </row>
+    <row r="528" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A528">
+        <v>13027</v>
+      </c>
+      <c r="B528">
+        <v>2024</v>
+      </c>
+      <c r="E528" t="s">
+        <v>1380</v>
+      </c>
+      <c r="F528" t="s">
+        <v>1383</v>
+      </c>
+      <c r="H528" t="s">
+        <v>1380</v>
+      </c>
+      <c r="J528" t="s">
+        <v>1380</v>
+      </c>
+      <c r="K528" t="s">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="529" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A529" s="6"/>
+      <c r="B529" s="6"/>
+      <c r="E529" s="6"/>
+      <c r="F529" s="6"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:S499" xr:uid="{00000000-0001-0000-0000-000000000000}">
